--- a/web_Hello_var_15/firstapp_var_15/tablica/purchase_log.xlsx
+++ b/web_Hello_var_15/firstapp_var_15/tablica/purchase_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,10 +457,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>21213</t>
-        </is>
+      <c r="A3" t="n">
+        <v>21213</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -471,6 +469,44 @@
         <v>313</v>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>Гарантия, Доставка, Сборка</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>313</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Корпус</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Гарантия, Доставка, Сборка</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>олег</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Процессор</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Гарантия, Доставка, Сборка</t>
         </is>
